--- a/lib/Tournement Data.xlsx
+++ b/lib/Tournement Data.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Code Project\Java\DebatTeam\lib\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CA5857-DED6-4176-94F7-EC26E19DFDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,8 +25,502 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="163">
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Entry</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Peninsula</t>
+  </si>
+  <si>
+    <t>CA/US</t>
+  </si>
+  <si>
+    <t>Farjami &amp; Weiss</t>
+  </si>
+  <si>
+    <t>Camron Farjami</t>
+  </si>
+  <si>
+    <t>Damien HS and St. Lucyâ€™s Priory</t>
+  </si>
+  <si>
+    <t>Mariano &amp; Duarte</t>
+  </si>
+  <si>
+    <t>DHASLP DM</t>
+  </si>
+  <si>
+    <t>Ortiz &amp; Vazquez</t>
+  </si>
+  <si>
+    <t>DHASLP OV</t>
+  </si>
+  <si>
+    <t>Parmar &amp; Mattera</t>
+  </si>
+  <si>
+    <t>DHASLP PM</t>
+  </si>
+  <si>
+    <t>Carlson &amp; Rudy</t>
+  </si>
+  <si>
+    <t>DHASLP RC</t>
+  </si>
+  <si>
+    <t>ModernBrain</t>
+  </si>
+  <si>
+    <t>Chen &amp; Xia</t>
+  </si>
+  <si>
+    <t>Ian Xia</t>
+  </si>
+  <si>
+    <t>IVA</t>
+  </si>
+  <si>
+    <t>Chagoya &amp; Fisk</t>
+  </si>
+  <si>
+    <t>IVA CF</t>
+  </si>
+  <si>
+    <t>Pan &amp; Yian</t>
+  </si>
+  <si>
+    <t>James Pan</t>
+  </si>
+  <si>
+    <t>La Reina</t>
+  </si>
+  <si>
+    <t>Basu &amp; Shah</t>
+  </si>
+  <si>
+    <t>LaRei BS</t>
+  </si>
+  <si>
+    <t>Meadows</t>
+  </si>
+  <si>
+    <t>NV/US</t>
+  </si>
+  <si>
+    <t>Krikorian &amp; Tselikis</t>
+  </si>
+  <si>
+    <t>Meadow KT</t>
+  </si>
+  <si>
+    <t>Mujtaba &amp; Cruz</t>
+  </si>
+  <si>
+    <t>Meadow MC</t>
+  </si>
+  <si>
+    <t>Chill &amp; Shu</t>
+  </si>
+  <si>
+    <t>Modern CS</t>
+  </si>
+  <si>
+    <t>Jiang &amp; Li</t>
+  </si>
+  <si>
+    <t>Modern JL</t>
+  </si>
+  <si>
+    <t>Jun &amp; Shu</t>
+  </si>
+  <si>
+    <t>Modern JS</t>
+  </si>
+  <si>
+    <t>Tan &amp; Zhao</t>
+  </si>
+  <si>
+    <t>Modern TZ</t>
+  </si>
+  <si>
+    <t>Notre Dame</t>
+  </si>
+  <si>
+    <t>Ballard &amp; Plotkin</t>
+  </si>
+  <si>
+    <t>NotDam BP</t>
+  </si>
+  <si>
+    <t>Duncan &amp; Norman</t>
+  </si>
+  <si>
+    <t>NotDam DN</t>
+  </si>
+  <si>
+    <t>Grisham &amp; Santos</t>
+  </si>
+  <si>
+    <t>NotDam GS</t>
+  </si>
+  <si>
+    <t>Gormley &amp; Kinsley</t>
+  </si>
+  <si>
+    <t>NotDam KG</t>
+  </si>
+  <si>
+    <t>Ching &amp; Milone</t>
+  </si>
+  <si>
+    <t>NotDam MC</t>
+  </si>
+  <si>
+    <t>Deng &amp; Pira</t>
+  </si>
+  <si>
+    <t>NotDam PD</t>
+  </si>
+  <si>
+    <t>Bhagat &amp; Wilner</t>
+  </si>
+  <si>
+    <t>Penins BW</t>
+  </si>
+  <si>
+    <t>Deng &amp; Kim</t>
+  </si>
+  <si>
+    <t>Penins DK</t>
+  </si>
+  <si>
+    <t>Gong &amp; Wilson</t>
+  </si>
+  <si>
+    <t>Penins GW</t>
+  </si>
+  <si>
+    <t>Liu &amp; Liu</t>
+  </si>
+  <si>
+    <t>Penins LL</t>
+  </si>
+  <si>
+    <t>Lu &amp; Ngo</t>
+  </si>
+  <si>
+    <t>Penins LN</t>
+  </si>
+  <si>
+    <t>San Marino</t>
+  </si>
+  <si>
+    <t>Louie &amp; Liang</t>
+  </si>
+  <si>
+    <t>SanMar LL</t>
+  </si>
+  <si>
+    <t>Tran &amp; Chou</t>
+  </si>
+  <si>
+    <t>SanMar TC</t>
+  </si>
+  <si>
+    <t>Paradigm</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>Last</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>Agustin</t>
+  </si>
+  <si>
+    <t>Hire</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Ava</t>
+  </si>
+  <si>
+    <t>Almand</t>
+  </si>
+  <si>
+    <t>Notre Dame High School</t>
+  </si>
+  <si>
+    <t>Joseph</t>
+  </si>
+  <si>
+    <t>Barragan</t>
+  </si>
+  <si>
+    <t>Jared</t>
+  </si>
+  <si>
+    <t>Burke</t>
+  </si>
+  <si>
+    <t>Peninsula High School</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Buscho</t>
+  </si>
+  <si>
+    <t>Sergio</t>
+  </si>
+  <si>
+    <t>Chavez</t>
+  </si>
+  <si>
+    <t>Cade</t>
+  </si>
+  <si>
+    <t>Cottrell</t>
+  </si>
+  <si>
+    <t>The Meadows School</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>Irina</t>
+  </si>
+  <si>
+    <t>Danova</t>
+  </si>
+  <si>
+    <t>Sophia</t>
+  </si>
+  <si>
+    <t>Demayo</t>
+  </si>
+  <si>
+    <t>Edward</t>
+  </si>
+  <si>
+    <t>Deng</t>
+  </si>
+  <si>
+    <t>Meher</t>
+  </si>
+  <si>
+    <t>Dhaliwal</t>
+  </si>
+  <si>
+    <t>Reid</t>
+  </si>
+  <si>
+    <t>Ehrlich-Quinn</t>
+  </si>
+  <si>
+    <t>Holly</t>
+  </si>
+  <si>
+    <t>Fena</t>
+  </si>
+  <si>
+    <t>Kaden</t>
+  </si>
+  <si>
+    <t>Grabowski</t>
+  </si>
+  <si>
+    <t>Hong</t>
+  </si>
+  <si>
+    <t>Mishelle</t>
+  </si>
+  <si>
+    <t>Kamyshnikov</t>
+  </si>
+  <si>
+    <t>Yueshuya</t>
+  </si>
+  <si>
+    <t>Li</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Louie</t>
+  </si>
+  <si>
+    <t>San Marino High School</t>
+  </si>
+  <si>
+    <t>Justin</t>
+  </si>
+  <si>
+    <t>Loza</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>Joshua</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Dylan</t>
+  </si>
+  <si>
+    <t>Michalak</t>
+  </si>
+  <si>
+    <t>Sabeeh</t>
+  </si>
+  <si>
+    <t>Mirza</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>Roan</t>
+  </si>
+  <si>
+    <t>Murphy</t>
+  </si>
+  <si>
+    <t>Curtis</t>
+  </si>
+  <si>
+    <t>Ortega</t>
+  </si>
+  <si>
+    <t>Chris</t>
+  </si>
+  <si>
+    <t>Paredes</t>
+  </si>
+  <si>
+    <t>Brandon</t>
+  </si>
+  <si>
+    <t>Logan</t>
+  </si>
+  <si>
+    <t>Park</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>Maddox</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Jason</t>
+  </si>
+  <si>
+    <t>Phan</t>
+  </si>
+  <si>
+    <t>Peter</t>
+  </si>
+  <si>
+    <t>Rayeed</t>
+  </si>
+  <si>
+    <t>Rahman</t>
+  </si>
+  <si>
+    <t>Ira</t>
+  </si>
+  <si>
+    <t>Sirulnick</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>Stroud</t>
+  </si>
+  <si>
+    <t>Malone</t>
+  </si>
+  <si>
+    <t>Urfalian</t>
+  </si>
+  <si>
+    <t>Teddy</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Wachtler</t>
+  </si>
+  <si>
+    <t>Rachel</t>
+  </si>
+  <si>
+    <t>Wear</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Steven</t>
+  </si>
+  <si>
+    <t>Yu</t>
+  </si>
+  <si>
+    <t>arman</t>
+  </si>
+  <si>
+    <t>omidvar</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -330,10 +831,1016 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98DB2CB3-21C9-41F1-846D-397ABF7086F5}">
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" t="s">
+        <v>105</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21" t="s">
+        <v>119</v>
+      </c>
+      <c r="E21" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" t="s">
+        <v>76</v>
+      </c>
+      <c r="F26" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+      <c r="F28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" t="s">
+        <v>138</v>
+      </c>
+      <c r="E29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>139</v>
+      </c>
+      <c r="D30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" t="s">
+        <v>141</v>
+      </c>
+      <c r="D31" t="s">
+        <v>138</v>
+      </c>
+      <c r="E31" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>142</v>
+      </c>
+      <c r="D32" t="s">
+        <v>143</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D34" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F34" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>149</v>
+      </c>
+      <c r="D36" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>151</v>
+      </c>
+      <c r="D37" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>153</v>
+      </c>
+      <c r="C38" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" t="s">
+        <v>155</v>
+      </c>
+      <c r="E38" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>159</v>
+      </c>
+      <c r="D40" t="s">
+        <v>160</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="F40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" t="s">
+        <v>162</v>
+      </c>
+      <c r="E41" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>